--- a/templates/GDA-FLC-028_gravedad_grueso.xlsx
+++ b/templates/GDA-FLC-028_gravedad_grueso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeoDelta Líneas\Dropbox\14. GEODELTA\014 FORMATOS ACTUALIZADOS 2026\FORMATOS PARA DIGITAR ACTUALIZADOS 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DCM-04\AppData\Local\Temp\claude\D--Documents-Prototipos-claude-code-interfaz\dc24a8ee-ce81-4bc3-875e-fdda07eddd40\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D9496E-2400-4160-807C-979D15DC6094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4EE19D0-F6A7-48BB-B9C5-22C6A2FD59BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1 (2)" sheetId="1" r:id="rId1"/>
@@ -2159,39 +2159,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2199,43 +2170,41 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2253,10 +2222,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2265,42 +2240,67 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2594,6 +2594,93 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>3424</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>196602</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Firma Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C53CB66-C53F-4C34-AC9B-5651E918C54F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect l="88188"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7343775" y="8337799"/>
+          <a:ext cx="2857500" cy="1136153"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>246748</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>467627</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Firma Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B319B96-DFE2-4930-BDFE-4077F0880533}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11314798" y="8334375"/>
+          <a:ext cx="1916329" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2852,21 +2939,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="166"/>
-      <c r="B1" s="167"/>
-      <c r="C1" s="171" t="s">
+      <c r="A1" s="193"/>
+      <c r="B1" s="194"/>
+      <c r="C1" s="196" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="172" t="s">
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="194"/>
+      <c r="I1" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="173"/>
-      <c r="K1" s="174"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="199"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="2"/>
@@ -2896,31 +2983,31 @@
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
-      <c r="AO1" s="175" t="s">
+      <c r="AO1" s="200" t="s">
         <v>2</v>
       </c>
-      <c r="AP1" s="176"/>
-      <c r="AQ1" s="176"/>
+      <c r="AP1" s="167"/>
+      <c r="AQ1" s="167"/>
       <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3"/>
     </row>
     <row r="2" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="168"/>
-      <c r="B2" s="151"/>
-      <c r="C2" s="177" t="s">
+      <c r="A2" s="180"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="201" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="178" t="s">
+      <c r="D2" s="179"/>
+      <c r="E2" s="179"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="179"/>
+      <c r="I2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="164"/>
-      <c r="K2" s="165"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="149"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
@@ -2958,19 +3045,19 @@
       <c r="AT2" s="3"/>
     </row>
     <row r="3" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="168"/>
-      <c r="B3" s="151"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="151"/>
-      <c r="H3" s="151"/>
-      <c r="I3" s="178" t="s">
+      <c r="A3" s="180"/>
+      <c r="B3" s="179"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="179"/>
+      <c r="I3" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="164"/>
-      <c r="K3" s="165"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="149"/>
       <c r="L3" s="1"/>
       <c r="M3" s="5" t="s">
         <v>6</v>
@@ -2994,12 +3081,12 @@
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
-      <c r="AG3" s="179" t="s">
+      <c r="AG3" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="AH3" s="176"/>
-      <c r="AI3" s="176"/>
-      <c r="AJ3" s="176"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="167"/>
+      <c r="AJ3" s="167"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
@@ -3018,19 +3105,19 @@
       <c r="AT3" s="3"/>
     </row>
     <row r="4" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="169"/>
-      <c r="B4" s="170"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="170"/>
-      <c r="F4" s="170"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="170"/>
-      <c r="I4" s="181" t="s">
+      <c r="A4" s="195"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="205" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="170"/>
-      <c r="K4" s="182"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="206"/>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -3052,10 +3139,10 @@
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
-      <c r="AG4" s="176"/>
-      <c r="AH4" s="176"/>
-      <c r="AI4" s="176"/>
-      <c r="AJ4" s="176"/>
+      <c r="AG4" s="167"/>
+      <c r="AH4" s="167"/>
+      <c r="AI4" s="167"/>
+      <c r="AJ4" s="167"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
@@ -3075,15 +3162,15 @@
     </row>
     <row r="5" spans="1:46" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="116"/>
-      <c r="B5" s="180"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
+      <c r="B5" s="204"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="179"/>
+      <c r="H5" s="179"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
       <c r="K5" s="117"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -3106,10 +3193,10 @@
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
-      <c r="AG5" s="176"/>
-      <c r="AH5" s="176"/>
-      <c r="AI5" s="176"/>
-      <c r="AJ5" s="176"/>
+      <c r="AG5" s="167"/>
+      <c r="AH5" s="167"/>
+      <c r="AI5" s="167"/>
+      <c r="AJ5" s="167"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
@@ -3132,17 +3219,17 @@
       <c r="B6" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="155"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="157" t="s">
+      <c r="C6" s="207"/>
+      <c r="D6" s="163"/>
+      <c r="E6" s="163"/>
+      <c r="F6" s="163"/>
+      <c r="G6" s="208" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="158"/>
-      <c r="I6" s="159"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="160"/>
+      <c r="H6" s="156"/>
+      <c r="I6" s="209"/>
+      <c r="J6" s="163"/>
+      <c r="K6" s="210"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="11" t="s">
@@ -3194,17 +3281,17 @@
       <c r="B7" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="209"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="161" t="s">
+      <c r="C7" s="144"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="146" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="162"/>
-      <c r="I7" s="163"/>
-      <c r="J7" s="164"/>
-      <c r="K7" s="165"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="149"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="11" t="s">
@@ -3256,17 +3343,17 @@
       <c r="B8" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="209"/>
-      <c r="D8" s="164"/>
-      <c r="E8" s="164"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="161" t="s">
+      <c r="C8" s="144"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="162"/>
-      <c r="I8" s="163"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="165"/>
+      <c r="H8" s="147"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="145"/>
+      <c r="K8" s="149"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1">
         <f>17-2.57</f>
@@ -3321,14 +3408,14 @@
       <c r="B9" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="209"/>
-      <c r="D9" s="164"/>
-      <c r="E9" s="164"/>
-      <c r="F9" s="164"/>
-      <c r="G9" s="161" t="s">
+      <c r="C9" s="144"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="146" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="162"/>
+      <c r="H9" s="147"/>
       <c r="I9" s="121" t="s">
         <v>22</v>
       </c>
@@ -3385,20 +3472,20 @@
       <c r="B10" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="209"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="214" t="s">
+      <c r="C10" s="144"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="215"/>
-      <c r="I10" s="209" t="str">
+      <c r="H10" s="159"/>
+      <c r="I10" s="144" t="str">
         <f>CONCATENATE(J9,," ",K9,"-",D12,"-",B44,F12)</f>
         <v xml:space="preserve"> --</v>
       </c>
-      <c r="J10" s="164"/>
-      <c r="K10" s="165"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="149"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="11" t="s">
@@ -3447,15 +3534,15 @@
     </row>
     <row r="11" spans="1:46" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="124"/>
-      <c r="B11" s="210"/>
-      <c r="C11" s="170"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="170"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="170"/>
-      <c r="H11" s="170"/>
-      <c r="I11" s="170"/>
-      <c r="J11" s="170"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="151"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="151"/>
+      <c r="J11" s="151"/>
       <c r="K11" s="125"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3510,10 +3597,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="216" t="s">
+      <c r="G12" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="158"/>
+      <c r="H12" s="156"/>
       <c r="I12" s="18"/>
       <c r="J12" s="19" t="s">
         <v>30</v>
@@ -3566,15 +3653,15 @@
       <c r="B13" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="209"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="164"/>
-      <c r="I13" s="164"/>
-      <c r="J13" s="164"/>
-      <c r="K13" s="165"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="149"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="11"/>
@@ -3726,19 +3813,19 @@
       <c r="AT15" s="3"/>
     </row>
     <row r="16" spans="1:46" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="211" t="s">
+      <c r="A16" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="212"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="212"/>
-      <c r="I16" s="212"/>
-      <c r="J16" s="212"/>
-      <c r="K16" s="213"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="153"/>
+      <c r="K16" s="154"/>
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -3838,13 +3925,13 @@
     <row r="18" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="129"/>
       <c r="B18" s="130"/>
-      <c r="C18" s="200" t="s">
+      <c r="C18" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="207"/>
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="157"/>
       <c r="H18" s="132"/>
       <c r="I18" s="132"/>
       <c r="J18" s="130"/>
@@ -3898,10 +3985,10 @@
     <row r="19" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="129"/>
       <c r="B19" s="130"/>
-      <c r="C19" s="206" t="s">
+      <c r="C19" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="203"/>
+      <c r="D19" s="162"/>
       <c r="E19" s="27" t="s">
         <v>36</v>
       </c>
@@ -4114,13 +4201,13 @@
     <row r="23" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="129"/>
       <c r="B23" s="130"/>
-      <c r="C23" s="200" t="s">
+      <c r="C23" s="155" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
-      <c r="G23" s="207"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="157"/>
       <c r="H23" s="130"/>
       <c r="I23" s="130"/>
       <c r="J23" s="130"/>
@@ -4172,11 +4259,11 @@
     <row r="24" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="129"/>
       <c r="B24" s="130"/>
-      <c r="C24" s="206" t="s">
+      <c r="C24" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="156"/>
-      <c r="E24" s="203"/>
+      <c r="D24" s="163"/>
+      <c r="E24" s="162"/>
       <c r="F24" s="40"/>
       <c r="G24" s="41" t="e">
         <f>G19/(G21-G20)</f>
@@ -4233,11 +4320,11 @@
     <row r="25" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="129"/>
       <c r="B25" s="130"/>
-      <c r="C25" s="144" t="s">
+      <c r="C25" s="164" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="164"/>
-      <c r="E25" s="146"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="165"/>
       <c r="F25" s="45"/>
       <c r="G25" s="46" t="e">
         <f>G21/(G21-G20)</f>
@@ -4283,11 +4370,11 @@
     <row r="26" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="129"/>
       <c r="B26" s="130"/>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="164" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="164"/>
-      <c r="E26" s="146"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="165"/>
       <c r="F26" s="45"/>
       <c r="G26" s="46" t="e">
         <f>G19/(G19-G20)</f>
@@ -4342,11 +4429,11 @@
     <row r="27" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="129"/>
       <c r="B27" s="130"/>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="164" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="164"/>
-      <c r="E27" s="146"/>
+      <c r="D27" s="145"/>
+      <c r="E27" s="165"/>
       <c r="F27" s="45" t="s">
         <v>49</v>
       </c>
@@ -4403,11 +4490,11 @@
     <row r="28" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="129"/>
       <c r="B28" s="130"/>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="164" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="164"/>
-      <c r="E28" s="146"/>
+      <c r="D28" s="145"/>
+      <c r="E28" s="165"/>
       <c r="F28" s="45" t="s">
         <v>51</v>
       </c>
@@ -4453,11 +4540,11 @@
     <row r="29" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="129"/>
       <c r="B29" s="130"/>
-      <c r="C29" s="144" t="s">
+      <c r="C29" s="164" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="164"/>
-      <c r="E29" s="146"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="165"/>
       <c r="F29" s="45" t="s">
         <v>53</v>
       </c>
@@ -4483,11 +4570,11 @@
       <c r="W29" s="23"/>
       <c r="X29" s="23"/>
       <c r="Y29" s="23"/>
-      <c r="Z29" s="144" t="s">
+      <c r="Z29" s="164" t="s">
         <v>54</v>
       </c>
-      <c r="AA29" s="145"/>
-      <c r="AB29" s="146"/>
+      <c r="AA29" s="211"/>
+      <c r="AB29" s="165"/>
       <c r="AC29" s="32" t="s">
         <v>55</v>
       </c>
@@ -4512,11 +4599,11 @@
     <row r="30" spans="1:46" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129"/>
       <c r="B30" s="130"/>
-      <c r="C30" s="147" t="s">
+      <c r="C30" s="212" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="148"/>
-      <c r="E30" s="149"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="214"/>
       <c r="F30" s="54" t="s">
         <v>57</v>
       </c>
@@ -4542,11 +4629,11 @@
       <c r="W30" s="23"/>
       <c r="X30" s="23"/>
       <c r="Y30" s="23"/>
-      <c r="Z30" s="144" t="s">
+      <c r="Z30" s="164" t="s">
         <v>58</v>
       </c>
-      <c r="AA30" s="145"/>
-      <c r="AB30" s="146"/>
+      <c r="AA30" s="211"/>
+      <c r="AB30" s="165"/>
       <c r="AC30" s="32" t="s">
         <v>37</v>
       </c>
@@ -4597,11 +4684,11 @@
       <c r="W31" s="23"/>
       <c r="X31" s="23"/>
       <c r="Y31" s="23"/>
-      <c r="Z31" s="144" t="s">
+      <c r="Z31" s="164" t="s">
         <v>59</v>
       </c>
-      <c r="AA31" s="145"/>
-      <c r="AB31" s="146"/>
+      <c r="AA31" s="211"/>
+      <c r="AB31" s="165"/>
       <c r="AC31" s="32" t="s">
         <v>37</v>
       </c>
@@ -4651,11 +4738,11 @@
       <c r="W32" s="62"/>
       <c r="X32" s="60"/>
       <c r="Y32" s="3"/>
-      <c r="Z32" s="144" t="s">
+      <c r="Z32" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="AA32" s="145"/>
-      <c r="AB32" s="146"/>
+      <c r="AA32" s="211"/>
+      <c r="AB32" s="165"/>
       <c r="AC32" s="32" t="s">
         <v>62</v>
       </c>
@@ -4712,11 +4799,11 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
-      <c r="Z33" s="144" t="s">
+      <c r="Z33" s="164" t="s">
         <v>63</v>
       </c>
-      <c r="AA33" s="145"/>
-      <c r="AB33" s="146"/>
+      <c r="AA33" s="211"/>
+      <c r="AB33" s="165"/>
       <c r="AC33" s="32" t="s">
         <v>64</v>
       </c>
@@ -4781,11 +4868,11 @@
       <c r="W34" s="64"/>
       <c r="X34" s="64"/>
       <c r="Y34" s="64"/>
-      <c r="Z34" s="144" t="s">
+      <c r="Z34" s="164" t="s">
         <v>68</v>
       </c>
-      <c r="AA34" s="145"/>
-      <c r="AB34" s="146"/>
+      <c r="AA34" s="211"/>
+      <c r="AB34" s="165"/>
       <c r="AC34" s="32" t="s">
         <v>69</v>
       </c>
@@ -4817,23 +4904,23 @@
       <c r="AT34" s="13"/>
     </row>
     <row r="35" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="150" t="s">
+      <c r="A35" s="215" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="151"/>
-      <c r="C35" s="151"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="152" t="s">
+      <c r="B35" s="179"/>
+      <c r="C35" s="179"/>
+      <c r="D35" s="179"/>
+      <c r="E35" s="179"/>
+      <c r="F35" s="183" t="s">
         <v>71</v>
       </c>
-      <c r="G35" s="151"/>
+      <c r="G35" s="179"/>
       <c r="H35" s="137"/>
-      <c r="I35" s="152" t="s">
+      <c r="I35" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="J35" s="151"/>
-      <c r="K35" s="153"/>
+      <c r="J35" s="179"/>
+      <c r="K35" s="184"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="65" t="e">
@@ -4854,11 +4941,11 @@
       <c r="W35" s="64"/>
       <c r="X35" s="64"/>
       <c r="Y35" s="64"/>
-      <c r="Z35" s="154" t="s">
+      <c r="Z35" s="216" t="s">
         <v>73</v>
       </c>
-      <c r="AA35" s="148"/>
-      <c r="AB35" s="149"/>
+      <c r="AA35" s="213"/>
+      <c r="AB35" s="214"/>
       <c r="AC35" s="36" t="s">
         <v>57</v>
       </c>
@@ -4890,13 +4977,13 @@
       <c r="AT35" s="13"/>
     </row>
     <row r="36" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="193" t="s">
+      <c r="A36" s="178" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="151"/>
-      <c r="C36" s="151"/>
-      <c r="D36" s="151"/>
-      <c r="E36" s="151"/>
+      <c r="B36" s="179"/>
+      <c r="C36" s="179"/>
+      <c r="D36" s="179"/>
+      <c r="E36" s="179"/>
       <c r="F36" s="139"/>
       <c r="G36" s="140"/>
       <c r="H36" s="137"/>
@@ -4949,11 +5036,11 @@
       <c r="AT36" s="13"/>
     </row>
     <row r="37" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="168"/>
-      <c r="B37" s="151"/>
-      <c r="C37" s="151"/>
-      <c r="D37" s="151"/>
-      <c r="E37" s="151"/>
+      <c r="A37" s="180"/>
+      <c r="B37" s="179"/>
+      <c r="C37" s="179"/>
+      <c r="D37" s="179"/>
+      <c r="E37" s="179"/>
       <c r="F37" s="141"/>
       <c r="G37" s="137"/>
       <c r="H37" s="137"/>
@@ -5006,11 +5093,11 @@
       <c r="AT37" s="13"/>
     </row>
     <row r="38" spans="1:46" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="168"/>
-      <c r="B38" s="151"/>
-      <c r="C38" s="151"/>
-      <c r="D38" s="151"/>
-      <c r="E38" s="151"/>
+      <c r="A38" s="180"/>
+      <c r="B38" s="179"/>
+      <c r="C38" s="179"/>
+      <c r="D38" s="179"/>
+      <c r="E38" s="179"/>
       <c r="F38" s="141"/>
       <c r="G38" s="137"/>
       <c r="H38" s="137"/>
@@ -5064,11 +5151,11 @@
       <c r="AT38" s="23"/>
     </row>
     <row r="39" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="168"/>
-      <c r="B39" s="151"/>
-      <c r="C39" s="151"/>
-      <c r="D39" s="151"/>
-      <c r="E39" s="151"/>
+      <c r="A39" s="180"/>
+      <c r="B39" s="179"/>
+      <c r="C39" s="179"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="179"/>
       <c r="F39" s="141"/>
       <c r="G39" s="140"/>
       <c r="H39" s="142"/>
@@ -5122,21 +5209,21 @@
       <c r="AT39" s="13"/>
     </row>
     <row r="40" spans="1:46" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="168"/>
-      <c r="B40" s="151"/>
-      <c r="C40" s="151"/>
-      <c r="D40" s="151"/>
-      <c r="E40" s="151"/>
-      <c r="F40" s="194" t="s">
+      <c r="A40" s="180"/>
+      <c r="B40" s="179"/>
+      <c r="C40" s="179"/>
+      <c r="D40" s="179"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="181" t="s">
         <v>77</v>
       </c>
-      <c r="G40" s="188"/>
+      <c r="G40" s="173"/>
       <c r="H40" s="142"/>
-      <c r="I40" s="194" t="s">
+      <c r="I40" s="181" t="s">
         <v>99</v>
       </c>
-      <c r="J40" s="188"/>
-      <c r="K40" s="195"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="182"/>
       <c r="L40" s="64"/>
       <c r="M40" s="64"/>
       <c r="N40" s="12"/>
@@ -5182,33 +5269,33 @@
       <c r="AT40" s="23"/>
     </row>
     <row r="41" spans="1:46" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="168"/>
-      <c r="B41" s="151"/>
-      <c r="C41" s="151"/>
-      <c r="D41" s="151"/>
-      <c r="E41" s="151"/>
-      <c r="F41" s="152" t="s">
+      <c r="A41" s="180"/>
+      <c r="B41" s="179"/>
+      <c r="C41" s="179"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="179"/>
+      <c r="F41" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="G41" s="151"/>
+      <c r="G41" s="179"/>
       <c r="H41" s="137"/>
-      <c r="I41" s="152" t="s">
+      <c r="I41" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="J41" s="151"/>
-      <c r="K41" s="153"/>
+      <c r="J41" s="179"/>
+      <c r="K41" s="184"/>
       <c r="L41" s="64"/>
       <c r="M41" s="64"/>
       <c r="N41" s="77">
         <f>N38/(N38-N39)</f>
         <v>1.5789473684210527</v>
       </c>
-      <c r="O41" s="208" t="s">
+      <c r="O41" s="166" t="s">
         <v>81</v>
       </c>
-      <c r="P41" s="176"/>
-      <c r="Q41" s="176"/>
-      <c r="R41" s="176"/>
+      <c r="P41" s="167"/>
+      <c r="Q41" s="167"/>
+      <c r="R41" s="167"/>
       <c r="S41" s="64"/>
       <c r="T41" s="64"/>
       <c r="U41" s="64"/>
@@ -5245,19 +5332,19 @@
       <c r="AT41" s="23"/>
     </row>
     <row r="42" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="196" t="s">
+      <c r="A42" s="185" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="197"/>
-      <c r="C42" s="197"/>
-      <c r="D42" s="197"/>
-      <c r="E42" s="197"/>
-      <c r="F42" s="197"/>
-      <c r="G42" s="197"/>
-      <c r="H42" s="197"/>
-      <c r="I42" s="197"/>
-      <c r="J42" s="197"/>
-      <c r="K42" s="198"/>
+      <c r="B42" s="186"/>
+      <c r="C42" s="186"/>
+      <c r="D42" s="186"/>
+      <c r="E42" s="186"/>
+      <c r="F42" s="186"/>
+      <c r="G42" s="186"/>
+      <c r="H42" s="186"/>
+      <c r="I42" s="186"/>
+      <c r="J42" s="186"/>
+      <c r="K42" s="187"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
@@ -5357,10 +5444,10 @@
     <row r="44" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="78"/>
-      <c r="C44" s="199" t="s">
+      <c r="C44" s="188" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="176"/>
+      <c r="D44" s="167"/>
       <c r="E44" s="78"/>
       <c r="F44" s="79" t="s">
         <v>84</v>
@@ -5415,8 +5502,8 @@
     <row r="45" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22"/>
       <c r="B45" s="22"/>
-      <c r="C45" s="176"/>
-      <c r="D45" s="176"/>
+      <c r="C45" s="167"/>
+      <c r="D45" s="167"/>
       <c r="E45" s="80"/>
       <c r="F45" s="22"/>
       <c r="G45" s="22"/>
@@ -5469,8 +5556,8 @@
     <row r="46" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22"/>
       <c r="B46" s="22"/>
-      <c r="C46" s="176"/>
-      <c r="D46" s="176"/>
+      <c r="C46" s="167"/>
+      <c r="D46" s="167"/>
       <c r="E46" s="80"/>
       <c r="F46" s="22"/>
       <c r="G46" s="22"/>
@@ -5523,8 +5610,8 @@
     <row r="47" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22"/>
       <c r="B47" s="22"/>
-      <c r="C47" s="176"/>
-      <c r="D47" s="176"/>
+      <c r="C47" s="167"/>
+      <c r="D47" s="167"/>
       <c r="E47" s="80"/>
       <c r="F47" s="22"/>
       <c r="G47" s="22"/>
@@ -5577,8 +5664,8 @@
     <row r="48" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22"/>
       <c r="B48" s="22"/>
-      <c r="C48" s="176"/>
-      <c r="D48" s="176"/>
+      <c r="C48" s="167"/>
+      <c r="D48" s="167"/>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
       <c r="G48" s="22"/>
@@ -5631,8 +5718,8 @@
     <row r="49" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22"/>
       <c r="B49" s="22"/>
-      <c r="C49" s="176"/>
-      <c r="D49" s="176"/>
+      <c r="C49" s="167"/>
+      <c r="D49" s="167"/>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
       <c r="G49" s="22"/>
@@ -5749,13 +5836,13 @@
       <c r="J51" s="22"/>
       <c r="K51" s="22"/>
       <c r="L51" s="22"/>
-      <c r="M51" s="200" t="s">
+      <c r="M51" s="155" t="s">
         <v>85</v>
       </c>
-      <c r="N51" s="158"/>
-      <c r="O51" s="158"/>
-      <c r="P51" s="158"/>
-      <c r="Q51" s="201"/>
+      <c r="N51" s="156"/>
+      <c r="O51" s="156"/>
+      <c r="P51" s="156"/>
+      <c r="Q51" s="189"/>
       <c r="R51" s="23"/>
       <c r="S51" s="23"/>
       <c r="T51" s="23"/>
@@ -5808,14 +5895,14 @@
       <c r="M52" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="N52" s="202" t="s">
+      <c r="N52" s="190" t="s">
         <v>87</v>
       </c>
-      <c r="O52" s="203"/>
-      <c r="P52" s="202" t="s">
+      <c r="O52" s="162"/>
+      <c r="P52" s="190" t="s">
         <v>88</v>
       </c>
-      <c r="Q52" s="204"/>
+      <c r="Q52" s="191"/>
       <c r="R52" s="23"/>
       <c r="S52" s="23"/>
       <c r="T52" s="23"/>
@@ -5868,13 +5955,13 @@
       <c r="M53" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="N53" s="205"/>
-      <c r="O53" s="184"/>
-      <c r="P53" s="205">
+      <c r="N53" s="192"/>
+      <c r="O53" s="169"/>
+      <c r="P53" s="192">
         <f>100-N53</f>
         <v>100</v>
       </c>
-      <c r="Q53" s="189"/>
+      <c r="Q53" s="174"/>
       <c r="R53" s="23"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
@@ -5924,15 +6011,15 @@
       <c r="J54" s="22"/>
       <c r="K54" s="22"/>
       <c r="L54" s="22"/>
-      <c r="M54" s="183" t="s">
+      <c r="M54" s="168" t="s">
         <v>89</v>
       </c>
-      <c r="N54" s="184"/>
-      <c r="O54" s="187" t="s">
+      <c r="N54" s="169"/>
+      <c r="O54" s="172" t="s">
         <v>90</v>
       </c>
-      <c r="P54" s="188"/>
-      <c r="Q54" s="189"/>
+      <c r="P54" s="173"/>
+      <c r="Q54" s="174"/>
       <c r="R54" s="23"/>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
@@ -5982,11 +6069,11 @@
       <c r="J55" s="22"/>
       <c r="K55" s="22"/>
       <c r="L55" s="22"/>
-      <c r="M55" s="185"/>
-      <c r="N55" s="186"/>
-      <c r="O55" s="190"/>
-      <c r="P55" s="191"/>
-      <c r="Q55" s="192"/>
+      <c r="M55" s="170"/>
+      <c r="N55" s="171"/>
+      <c r="O55" s="175"/>
+      <c r="P55" s="176"/>
+      <c r="Q55" s="177"/>
       <c r="R55" s="23"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
@@ -52354,28 +52441,33 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="O41:R41"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="Z31:AB31"/>
+    <mergeCell ref="Z32:AB32"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="AO1:AQ1"/>
+    <mergeCell ref="C2:H4"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="AG3:AJ5"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="M54:N55"/>
     <mergeCell ref="O54:Q55"/>
     <mergeCell ref="A36:E41"/>
@@ -52390,33 +52482,28 @@
     <mergeCell ref="P52:Q52"/>
     <mergeCell ref="N53:O53"/>
     <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="AO1:AQ1"/>
-    <mergeCell ref="C2:H4"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="AG3:AJ5"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="Z29:AB29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="Z31:AB31"/>
-    <mergeCell ref="Z32:AB32"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="O41:R41"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="G9:H9"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:D12 G19:G21 AD29:AD31 M53:N53 P53">
     <cfRule type="containsBlanks" dxfId="7" priority="2">
